--- a/python-in-excel-data-structures-demo.xlsx
+++ b/python-in-excel-data-structures-demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D40312-4F38-4724-A0E8-5D38C9A535E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFD436A-605F-4B40-9918-9EC5F883E625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -22,13 +22,44 @@
     <sheet name="5. pandas Series" sheetId="7" r:id="rId7"/>
     <sheet name="6. pandas DataFrame" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
+<python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
+  <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
+    <initialization>
+      <code xml:space="preserve">import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+import seaborn as sns
+import statsmodels as sm
+import excel
+import warnings
+warnings.simplefilter('ignore')
+excel.set_xl_scalar_conversion(excel.convert_to_scalar)
+excel.set_xl_array_conversion(excel.convert_to_dataframe)
+</code>
+    </initialization>
+  </environmentDefinition>
+</python>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
